--- a/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
+++ b/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5347A2-F104-46E7-AB92-A90E6FD0C2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19490" yWindow="660" windowWidth="17280" windowHeight="8880" xr2:uid="{4010788E-9D57-4518-8E30-3FC23E7ECB45}"/>
+    <workbookView xWindow="21710" yWindow="1130" windowWidth="17280" windowHeight="8880" xr2:uid="{4010788E-9D57-4518-8E30-3FC23E7ECB45}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
+++ b/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ferna\Documents\dev\Finscore\FinScore\V. 2 (Pudim)\dados_teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5347A2-F104-46E7-AB92-A90E6FD0C2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F78262D-6D8B-4891-929D-3AD08CD58D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21710" yWindow="1130" windowWidth="17280" windowHeight="8880" xr2:uid="{4010788E-9D57-4518-8E30-3FC23E7ECB45}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4010788E-9D57-4518-8E30-3FC23E7ECB45}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>SIMULAÇÕES FINSCORE</t>
   </si>
@@ -155,12 +155,6 @@
     <t>BRIGADEIRO</t>
   </si>
   <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>PUDIM DE LEITE (V2.00.07)</t>
-  </si>
-  <si>
     <t>Serasa em 700</t>
   </si>
   <si>
@@ -174,13 +168,19 @@
   </si>
   <si>
     <t>não roda: motivo desconhecido.</t>
+  </si>
+  <si>
+    <t>PUDIM (V2.00.07)</t>
+  </si>
+  <si>
+    <t>PUDIM (V2.00.12)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,8 +204,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,8 +240,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -242,11 +276,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -257,22 +317,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -609,528 +715,680 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FCEEB7-B92B-4053-9C51-209D00D628B8}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="44.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="73.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="32.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.88671875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E2" s="1" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="I3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="K3" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1">
-        <v>240</v>
-      </c>
-      <c r="E4" s="8">
-        <v>401.22</v>
-      </c>
-      <c r="F4" s="8">
-        <v>572.29</v>
-      </c>
-      <c r="G4" s="8">
-        <v>332.11</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6" t="str">
+      <c r="C4" s="5" t="str">
         <f>_xlfn.CONCAT(A4,RIGHT(B4,30))</f>
         <v>1Callamarys</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="D4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5">
+        <v>240</v>
+      </c>
+      <c r="F4" s="8">
+        <v>401.22</v>
+      </c>
+      <c r="G4" s="19">
+        <v>572.29</v>
+      </c>
+      <c r="H4" s="19">
+        <v>332.11</v>
+      </c>
+      <c r="I4" s="11">
+        <v>394.43</v>
+      </c>
+      <c r="J4" s="22">
+        <v>629.49</v>
+      </c>
+      <c r="K4" s="22">
+        <v>291.85000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="str">
+        <f>_xlfn.CONCAT(A5,RIGHT(B5,30))</f>
+        <v>2Cool Seed</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="5">
         <v>392.5</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="9">
         <v>644.94000000000005</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="20">
         <v>639.71</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="20">
         <v>652.44000000000005</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="str">
-        <f t="shared" ref="I5:I20" si="0">_xlfn.CONCAT(A5,RIGHT(B5,30))</f>
-        <v>2Cool Seed</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="I5" s="12">
+        <v>731.87</v>
+      </c>
+      <c r="J5" s="23">
+        <v>726.36</v>
+      </c>
+      <c r="K5" s="23">
+        <v>741.14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="str">
+        <f>_xlfn.CONCAT(A6,RIGHT(B6,30))</f>
+        <v>3 Cofesa - Super G Supermercado</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="5">
         <v>200</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="9">
         <v>649.04</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="20">
         <v>585.73</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="20">
         <v>748.18</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>3 Cofesa - Super G Supermercado</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="I6" s="12">
+        <v>726.56</v>
+      </c>
+      <c r="J6" s="23">
+        <v>647.85</v>
+      </c>
+      <c r="K6" s="23">
+        <v>874.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="str">
+        <f>_xlfn.CONCAT(A7,RIGHT(B7,30))</f>
+        <v>4t - E-Construmarket Tecnologia</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="5">
         <v>650</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="9">
         <v>666.28</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="20">
         <v>624.88</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="20">
         <v>728.84</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>4t - E-Construmarket Tecnologia</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="I7" s="12">
+        <v>747.93</v>
+      </c>
+      <c r="J7" s="23">
+        <v>705.02</v>
+      </c>
+      <c r="K7" s="23">
+        <v>824.09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="5" t="str">
+        <f>_xlfn.CONCAT(A8,RIGHT(B8,30))</f>
+        <v>5umarket - Mobicloud Tecnologia</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="5">
         <v>905</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="9">
         <v>766.21</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="20">
         <v>785</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="20">
         <v>758.54</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>5umarket - Mobicloud Tecnologia</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="I8" s="12">
+        <v>897.64</v>
+      </c>
+      <c r="J8" s="23">
+        <v>927.28</v>
+      </c>
+      <c r="K8" s="23">
+        <v>883.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="str">
+        <f>_xlfn.CONCAT(A9,RIGHT(B9,30))</f>
+        <v>6strumarket - SSA-Miro Solucoes</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="5">
         <v>255</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="9">
         <v>481.89</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="20">
         <v>394.89</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="20">
         <v>630.73</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>6strumarket - SSA-Miro Solucoes</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="I9" s="12">
+        <v>500</v>
+      </c>
+      <c r="J9" s="23">
+        <v>435.65</v>
+      </c>
+      <c r="K9" s="23">
+        <v>734.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="5" t="str">
+        <f>_xlfn.CONCAT(A10,RIGHT(B10,30))</f>
+        <v>7ornax - Flammers Participacoes</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="5">
         <v>475</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>7ornax - Flammers Participacoes</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="F10" s="24">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0</v>
+      </c>
+      <c r="I10" s="25">
+        <v>0</v>
+      </c>
+      <c r="J10" s="25">
+        <v>0</v>
+      </c>
+      <c r="K10" s="25">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="str">
+        <f>_xlfn.CONCAT(A11,RIGHT(B11,30))</f>
+        <v>8po Fornax - Fornax Consultoria</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="5">
         <v>227.5</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="9">
         <v>737.56</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="20">
         <v>809.47</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="20">
         <v>715.79</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>8po Fornax - Fornax Consultoria</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="I11" s="12">
+        <v>854.01</v>
+      </c>
+      <c r="J11" s="23">
+        <v>961.69</v>
+      </c>
+      <c r="K11" s="23">
+        <v>808.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
         <v>9</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="str">
+        <f>_xlfn.CONCAT(A12,RIGHT(B12,30))</f>
+        <v>9rupo Fornax - Modo Serviços RH</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="5">
         <v>790</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="9">
         <v>350</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="20">
         <v>825.62</v>
       </c>
-      <c r="G12" s="6">
+      <c r="H12" s="20">
         <v>295.19</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>9rupo Fornax - Modo Serviços RH</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="I12" s="12">
+        <v>350</v>
+      </c>
+      <c r="J12" s="23">
+        <v>925</v>
+      </c>
+      <c r="K12" s="23">
+        <v>221.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="5" t="str">
+        <f>_xlfn.CONCAT(A13,RIGHT(B13,30))</f>
+        <v>10upo Fornax - Mooven Assessoria</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="5">
         <v>902.5</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="9">
         <v>249.87</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="20">
         <v>428.95</v>
       </c>
-      <c r="G13" s="6">
+      <c r="H13" s="20">
         <v>190.55</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>10upo Fornax - Mooven Assessoria</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="I13" s="12">
+        <v>244.87</v>
+      </c>
+      <c r="J13" s="23">
+        <v>443.16</v>
+      </c>
+      <c r="K13" s="23">
+        <v>170.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="str">
+        <f>_xlfn.CONCAT(A14,RIGHT(B14,30))</f>
+        <v>11Grupo JNP - JNH Hoteis</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="5">
         <v>767.5</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="9">
         <v>532.41</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="20">
         <v>747.52</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="20">
         <v>454.01</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>11Grupo JNP - JNH Hoteis</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="I14" s="12">
+        <v>602.53</v>
+      </c>
+      <c r="J14" s="23">
+        <v>875.11</v>
+      </c>
+      <c r="K14" s="23">
+        <v>486.21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="str">
+        <f>_xlfn.CONCAT(A15,RIGHT(B15,30))</f>
+        <v>12Grupo JNP - JNS Seguradora</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="5">
         <v>587.5</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="9">
         <v>390.38</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="20">
         <v>373.08</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="20">
         <v>416.08</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>12Grupo JNP - JNS Seguradora</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="I15" s="12">
+        <v>376.14</v>
+      </c>
+      <c r="J15" s="23">
+        <v>356</v>
+      </c>
+      <c r="K15" s="23">
+        <v>411.72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>13</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="str">
+        <f>_xlfn.CONCAT(A16,RIGHT(B16,30))</f>
+        <v>13 - Mega Administradora de Bens</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="5">
         <v>157.5</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="9">
         <v>732.81</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="20">
         <v>720.04</v>
       </c>
-      <c r="G16" s="6">
+      <c r="H16" s="20">
         <v>751.29</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>13 - Mega Administradora de Bens</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="I16" s="12">
+        <v>845.81</v>
+      </c>
+      <c r="J16" s="23">
+        <v>836.2</v>
+      </c>
+      <c r="K16" s="23">
+        <v>862.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="5" t="str">
+        <f>_xlfn.CONCAT(A17,RIGHT(B17,30))</f>
+        <v>14Motos - Mega Motos Com Imp Exp</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="5">
         <v>847.5</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="9">
         <v>560.29</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="20">
         <v>623.65</v>
       </c>
-      <c r="G17" s="6">
+      <c r="H17" s="20">
         <v>530.13</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>14Motos - Mega Motos Com Imp Exp</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="I17" s="12">
+        <v>621.24</v>
+      </c>
+      <c r="J17" s="23">
+        <v>701.43</v>
+      </c>
+      <c r="K17" s="23">
+        <v>576.78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
         <v>15</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="str">
+        <f>_xlfn.CONCAT(A18,RIGHT(B18,30))</f>
+        <v>15Log Road Transporte Rodoviario</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="5">
         <v>717.5</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>15Log Road Transporte Rodoviario</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="F18" s="24">
+        <v>0</v>
+      </c>
+      <c r="G18" s="24">
+        <v>0</v>
+      </c>
+      <c r="H18" s="24">
+        <v>0</v>
+      </c>
+      <c r="I18" s="25">
+        <v>0</v>
+      </c>
+      <c r="J18" s="25">
+        <v>0</v>
+      </c>
+      <c r="K18" s="25">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="5" t="str">
+        <f>_xlfn.CONCAT(A19,RIGHT(B19,30))</f>
+        <v>16og Road - TMDL Armazens Gerais</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="5">
         <v>295</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="9">
         <v>752.8</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="20">
         <v>829.87</v>
       </c>
-      <c r="G19" s="6">
+      <c r="H19" s="20">
         <v>716.04</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>16og Road - TMDL Armazens Gerais</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="I19" s="12">
+        <v>837.55</v>
+      </c>
+      <c r="J19" s="23">
+        <v>989.67</v>
+      </c>
+      <c r="K19" s="23">
+        <v>755.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
         <v>17</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="5" t="str">
+        <f>_xlfn.CONCAT(A20,RIGHT(B20,30))</f>
+        <v>17Pacto Energia</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="5">
         <v>855</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="9">
         <v>312.61</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="20">
         <v>271.17</v>
       </c>
-      <c r="G20" s="6">
+      <c r="H20" s="20">
         <v>385.63</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>17Pacto Energia</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E22" s="1">
-        <f>CORREL(D4:D20,E4:E20)</f>
-        <v>-0.43574878517302107</v>
+      <c r="I20" s="12">
+        <v>289.87</v>
+      </c>
+      <c r="J20" s="23">
+        <v>245.52</v>
+      </c>
+      <c r="K20" s="23">
+        <v>397.45</v>
       </c>
     </row>
   </sheetData>

--- a/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
+++ b/V. 2 (Pudim)/dados_teste/RESULTADOS TESTES COMPARATIVOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ferna\Documents\dev\Finscore\FinScore\V. 2 (Pudim)\dados_teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F78262D-6D8B-4891-929D-3AD08CD58D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B862AD-25A7-41C3-BB05-1E1B5123E2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4010788E-9D57-4518-8E30-3FC23E7ECB45}"/>
   </bookViews>
@@ -396,6 +396,1295 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRIGADEIRO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$B$4:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Callamarys</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cool Seed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grupo Cofesa - Super G Supermercado</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Grupo E-Construmarket - E-Construmarket Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Grupo E-Construmarket - Mobicloud Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Grupo E-Construmarket - SSA-Miro Solucoes</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Grupo Fornax - Flammers Participacoes</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Grupo Fornax - Fornax Consultoria</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Grupo Fornax - Modo Serviços RH</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Grupo Fornax - Mooven Assessoria</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Grupo JNP - JNH Hoteis</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Grupo JNP - JNS Seguradora</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Grupo Mega Motos - Mega Administradora de Bens</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Grupo Mega Motos - Mega Motos Com Imp Exp</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Grupo TMDL-Log Road - Log Road Transporte Rodoviario</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Grupo TMDL-Log Road - TMDL Armazens Gerais</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Pacto Energia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$E$4:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>392.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>227.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>902.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>767.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>587.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>157.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>847.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>717.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>855</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0429-43E4-A58E-8149C6662440}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="2087764912"/>
+        <c:axId val="2083699120"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PUDIM (V2.00.07)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$B$4:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Callamarys</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cool Seed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grupo Cofesa - Super G Supermercado</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Grupo E-Construmarket - E-Construmarket Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Grupo E-Construmarket - Mobicloud Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Grupo E-Construmarket - SSA-Miro Solucoes</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Grupo Fornax - Flammers Participacoes</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Grupo Fornax - Fornax Consultoria</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Grupo Fornax - Modo Serviços RH</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Grupo Fornax - Mooven Assessoria</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Grupo JNP - JNH Hoteis</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Grupo JNP - JNS Seguradora</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Grupo Mega Motos - Mega Administradora de Bens</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Grupo Mega Motos - Mega Motos Com Imp Exp</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Grupo TMDL-Log Road - Log Road Transporte Rodoviario</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Grupo TMDL-Log Road - TMDL Armazens Gerais</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Pacto Energia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$F$4:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>401.22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>644.94000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>649.04</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>666.28</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>766.21</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>481.89</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>737.56</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>249.87</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>532.41</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>390.38</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>732.81</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>560.29</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>752.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>312.61</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0429-43E4-A58E-8149C6662440}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PUDIM (V2.00.12)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$B$4:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>Callamarys</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Cool Seed</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grupo Cofesa - Super G Supermercado</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Grupo E-Construmarket - E-Construmarket Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Grupo E-Construmarket - Mobicloud Tecnologia</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Grupo E-Construmarket - SSA-Miro Solucoes</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Grupo Fornax - Flammers Participacoes</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Grupo Fornax - Fornax Consultoria</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Grupo Fornax - Modo Serviços RH</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Grupo Fornax - Mooven Assessoria</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Grupo JNP - JNH Hoteis</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Grupo JNP - JNS Seguradora</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Grupo Mega Motos - Mega Administradora de Bens</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Grupo Mega Motos - Mega Motos Com Imp Exp</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Grupo TMDL-Log Road - Log Road Transporte Rodoviario</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Grupo TMDL-Log Road - TMDL Armazens Gerais</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Pacto Energia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$I$4:$I$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>394.43</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>731.87</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>726.56</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>747.93</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>897.64</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>854.01</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>244.87</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>602.53</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>376.14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>845.81</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>621.24</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>837.55</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>289.87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0429-43E4-A58E-8149C6662440}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="2087764912"/>
+        <c:axId val="2083699120"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2087764912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2083699120"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2083699120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2087764912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>531948</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>161470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>281213</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>81642</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46ECCCF6-9CAD-1E7A-4F7C-42D6658CC089}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -781,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>_xlfn.CONCAT(A4,RIGHT(B4,30))</f>
+        <f t="shared" ref="C4:C20" si="0">_xlfn.CONCAT(A4,RIGHT(B4,30))</f>
         <v>1Callamarys</v>
       </c>
       <c r="D4" s="14" t="s">
@@ -817,7 +2106,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>_xlfn.CONCAT(A5,RIGHT(B5,30))</f>
+        <f t="shared" si="0"/>
         <v>2Cool Seed</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -853,7 +2142,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>_xlfn.CONCAT(A6,RIGHT(B6,30))</f>
+        <f t="shared" si="0"/>
         <v>3 Cofesa - Super G Supermercado</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -889,7 +2178,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>_xlfn.CONCAT(A7,RIGHT(B7,30))</f>
+        <f t="shared" si="0"/>
         <v>4t - E-Construmarket Tecnologia</v>
       </c>
       <c r="D7" s="14" t="s">
@@ -925,7 +2214,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>_xlfn.CONCAT(A8,RIGHT(B8,30))</f>
+        <f t="shared" si="0"/>
         <v>5umarket - Mobicloud Tecnologia</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -961,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>_xlfn.CONCAT(A9,RIGHT(B9,30))</f>
+        <f t="shared" si="0"/>
         <v>6strumarket - SSA-Miro Solucoes</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -997,7 +2286,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>_xlfn.CONCAT(A10,RIGHT(B10,30))</f>
+        <f t="shared" si="0"/>
         <v>7ornax - Flammers Participacoes</v>
       </c>
       <c r="D10" s="14" t="s">
@@ -1036,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>_xlfn.CONCAT(A11,RIGHT(B11,30))</f>
+        <f t="shared" si="0"/>
         <v>8po Fornax - Fornax Consultoria</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -1072,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>_xlfn.CONCAT(A12,RIGHT(B12,30))</f>
+        <f t="shared" si="0"/>
         <v>9rupo Fornax - Modo Serviços RH</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -1108,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>_xlfn.CONCAT(A13,RIGHT(B13,30))</f>
+        <f t="shared" si="0"/>
         <v>10upo Fornax - Mooven Assessoria</v>
       </c>
       <c r="D13" s="14" t="s">
@@ -1144,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>_xlfn.CONCAT(A14,RIGHT(B14,30))</f>
+        <f t="shared" si="0"/>
         <v>11Grupo JNP - JNH Hoteis</v>
       </c>
       <c r="D14" s="14" t="s">
@@ -1180,7 +2469,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>_xlfn.CONCAT(A15,RIGHT(B15,30))</f>
+        <f t="shared" si="0"/>
         <v>12Grupo JNP - JNS Seguradora</v>
       </c>
       <c r="D15" s="14" t="s">
@@ -1216,7 +2505,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f>_xlfn.CONCAT(A16,RIGHT(B16,30))</f>
+        <f t="shared" si="0"/>
         <v>13 - Mega Administradora de Bens</v>
       </c>
       <c r="D16" s="14" t="s">
@@ -1252,7 +2541,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>_xlfn.CONCAT(A17,RIGHT(B17,30))</f>
+        <f t="shared" si="0"/>
         <v>14Motos - Mega Motos Com Imp Exp</v>
       </c>
       <c r="D17" s="14" t="s">
@@ -1288,7 +2577,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="5" t="str">
-        <f>_xlfn.CONCAT(A18,RIGHT(B18,30))</f>
+        <f t="shared" si="0"/>
         <v>15Log Road Transporte Rodoviario</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -1327,7 +2616,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="5" t="str">
-        <f>_xlfn.CONCAT(A19,RIGHT(B19,30))</f>
+        <f t="shared" si="0"/>
         <v>16og Road - TMDL Armazens Gerais</v>
       </c>
       <c r="D19" s="14" t="s">
@@ -1363,7 +2652,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="5" t="str">
-        <f>_xlfn.CONCAT(A20,RIGHT(B20,30))</f>
+        <f t="shared" si="0"/>
         <v>17Pacto Energia</v>
       </c>
       <c r="D20" s="14" t="s">
@@ -1394,5 +2683,6 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>